--- a/US/US_Producto.xlsx
+++ b/US/US_Producto.xlsx
@@ -2801,13 +2801,13 @@
         <v>0.01851796559967133</v>
       </c>
       <c r="L2" s="2">
-        <v>112.2262160580291</v>
+        <v>113.9149343886617</v>
       </c>
       <c r="M2" s="2">
-        <v>0.5195503020859663</v>
+        <v>0.5273682090745134</v>
       </c>
       <c r="N2" s="2">
-        <v>0.02078201208343865</v>
+        <v>0.02109472836298054</v>
       </c>
     </row>
     <row r="3" spans="1:14">
